--- a/sources/jin_step10.xlsx
+++ b/sources/jin_step10.xlsx
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 0</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>f~N,d ~df+2 -</t>
+          <t>f~N,d~df+2 -</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 0</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1 1 1 0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>0 1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">

--- a/sources/jin_step10.xlsx
+++ b/sources/jin_step10.xlsx
@@ -1037,6 +1037,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -1094,6 +1099,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -1156,6 +1166,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -1218,6 +1233,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -1280,6 +1300,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -1342,6 +1367,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1414,6 +1444,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1481,6 +1516,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1546,6 +1586,11 @@
       <c r="W16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -12044,6 +12089,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="AB129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -12096,6 +12146,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="AB130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -12148,6 +12203,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="AB131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -12200,6 +12260,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="AB132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -12252,6 +12317,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="AB133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -12304,6 +12374,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="AB134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -12356,6 +12431,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="AB135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -12408,6 +12488,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="AB136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -12460,6 +12545,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="AB137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -12510,6 +12600,11 @@
       <c r="U138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
